--- a/c/assignment2/Complexity_Chart (1).xlsx
+++ b/c/assignment2/Complexity_Chart (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alisha Garg\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alisha Garg\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B511CA-2CB4-4EDA-A697-C0C042A253DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C40519-F673-474C-8E30-9D6CDC1AE57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
   <si>
     <t xml:space="preserve">Bubble Sort </t>
   </si>
@@ -70,38 +70,17 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>Bubble Sort:</t>
+    <t>Insertion</t>
   </si>
   <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Ascending</t>
-  </si>
-  <si>
-    <t>Descending</t>
-  </si>
-  <si>
-    <t>Insertion Sort:</t>
-  </si>
-  <si>
-    <t>Selection Sort:</t>
-  </si>
-  <si>
-    <t>Quick Sort:</t>
-  </si>
-  <si>
-    <t>Merge Sort:</t>
-  </si>
-  <si>
-    <t>Heap Sort:</t>
+    <t>Heap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -145,14 +124,28 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -169,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -256,17 +249,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -282,21 +264,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -307,6 +280,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -356,30 +334,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>72.472999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>177.291</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>352.012</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>605.02300000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>956.49599999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1346.9079999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1816.809</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2338.7570000000001</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -409,30 +363,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.4999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.9E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.3E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.5000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.9000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -462,30 +392,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>73.465000000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>167.935</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>298.31299999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>467.142</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>672.33799999999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>896.46699999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1171.1890000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1508.0719999999999</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -705,30 +611,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>23.056000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>51.765000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>82.046999999999997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>123.928</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>172.91200000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>221.95699999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>322.48500000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>379.65100000000001</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -758,30 +640,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1.2999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.9E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.5000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.9E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.5999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.2999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.122</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -811,30 +669,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>38.313000000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>86.817999999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>148.87899999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>225.494</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>326.51</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>466.74799999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>585.64200000000005</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>780.79</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1054,30 +888,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>33.103999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>72.576999999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>117.86</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>185.93700000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>261.738</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>357.19400000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>466.34899999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>595.48099999999999</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1107,30 +917,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>28.675000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>63.32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>115.587</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>175.24199999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>259.67599999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>350.94</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>459.60300000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>599.221</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1160,30 +946,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>28.757999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>64.200999999999993</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>119.71299999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>188.38300000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>274.63200000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>369.553</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>512.48</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>599.27700000000004</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1403,30 +1165,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1.181</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.8069999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.5720000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.2149999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.5449999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.452</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.2050000000000001</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1456,30 +1194,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>67.837999999999994</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>176.26499999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>246.90899999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>386.03300000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>564.02700000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>744.77599999999995</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>976.27200000000005</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1307.578</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1509,30 +1223,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>45.11</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>94.897999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>165.846</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>268.125</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>378.58699999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>544.23199999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>700.28</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>879.33699999999999</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1752,30 +1442,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1.7989999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.5249999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.6989999999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.7939999999999996</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.375</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.7030000000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7.6680000000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.798</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1805,30 +1471,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.78800000000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0760000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.4350000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.915</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.5329999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.1589999999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.956</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.5310000000000001</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1858,30 +1500,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.81899999999999995</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.93700000000000006</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.3340000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4690000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.397</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.9450000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.66</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.4079999999999999</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2101,30 +1719,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>2.3039999999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.1040000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.8600000000000003</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.4379999999999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.1029999999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.944</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.1750000000000007</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9.5939999999999994</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2154,30 +1748,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1.9810000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.3029999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.524</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.9849999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.464</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.7040000000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.0529999999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.6550000000000002</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2207,30 +1777,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1.734</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.5680000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.8069999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.2170000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.6920000000000002</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.2189999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.218</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.7</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3865,32 +3411,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="17" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="17" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="O1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
+      <c r="A2" s="13"/>
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
@@ -3927,31 +3483,83 @@
       <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="18">
+        <v>0</v>
+      </c>
+      <c r="R3" s="18">
+        <v>0</v>
+      </c>
+      <c r="S3" s="18">
+        <v>0</v>
+      </c>
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
@@ -3960,155 +3568,477 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>8000</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="B4" s="11">
+        <v>33.103999999999999</v>
+      </c>
+      <c r="C4" s="11">
+        <v>28.675000000000001</v>
+      </c>
+      <c r="D4" s="11">
+        <v>28.757999999999999</v>
+      </c>
+      <c r="E4" s="11">
+        <v>72.472999999999999</v>
+      </c>
+      <c r="F4" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G4" s="11">
+        <v>73.465000000000003</v>
+      </c>
+      <c r="H4" s="11">
+        <v>1.7989999999999999</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="K4" s="11">
+        <v>1.181</v>
+      </c>
+      <c r="L4" s="11">
+        <v>67.837999999999994</v>
+      </c>
+      <c r="M4" s="11">
+        <v>45.11</v>
+      </c>
+      <c r="N4" s="11">
+        <v>23.056000000000001</v>
+      </c>
+      <c r="O4" s="11">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="P4" s="11">
+        <v>38.313000000000002</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>2.3039999999999998</v>
+      </c>
+      <c r="R4" s="11">
+        <v>1.9810000000000001</v>
+      </c>
+      <c r="S4" s="11">
+        <v>1.734</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
         <v>12000</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="B5" s="11">
+        <v>72.576999999999998</v>
+      </c>
+      <c r="C5" s="11">
+        <v>63.32</v>
+      </c>
+      <c r="D5" s="11">
+        <v>64.200999999999993</v>
+      </c>
+      <c r="E5" s="11">
+        <v>177.291</v>
+      </c>
+      <c r="F5" s="11">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="G5" s="11">
+        <v>167.935</v>
+      </c>
+      <c r="H5" s="11">
+        <v>2.5249999999999999</v>
+      </c>
+      <c r="I5" s="11">
+        <v>1.0760000000000001</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="K5" s="11">
+        <v>2.02</v>
+      </c>
+      <c r="L5" s="11">
+        <v>176.26499999999999</v>
+      </c>
+      <c r="M5" s="11">
+        <v>94.897999999999996</v>
+      </c>
+      <c r="N5" s="11">
+        <v>51.765000000000001</v>
+      </c>
+      <c r="O5" s="11">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P5" s="11">
+        <v>86.817999999999998</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="R5" s="11">
+        <v>1.3029999999999999</v>
+      </c>
+      <c r="S5" s="11">
+        <v>1.5680000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
         <v>16000</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="B6" s="11">
+        <v>117.86</v>
+      </c>
+      <c r="C6" s="11">
+        <v>115.587</v>
+      </c>
+      <c r="D6" s="11">
+        <v>119.71299999999999</v>
+      </c>
+      <c r="E6" s="11">
+        <v>352.012</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>298.31299999999999</v>
+      </c>
+      <c r="H6" s="11">
+        <v>3.6989999999999998</v>
+      </c>
+      <c r="I6" s="11">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1.3340000000000001</v>
+      </c>
+      <c r="K6" s="11">
+        <v>2.8069999999999999</v>
+      </c>
+      <c r="L6" s="11">
+        <v>246.90899999999999</v>
+      </c>
+      <c r="M6" s="11">
+        <v>165.846</v>
+      </c>
+      <c r="N6" s="11">
+        <v>82.046999999999997</v>
+      </c>
+      <c r="O6" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P6" s="11">
+        <v>148.87899999999999</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="R6" s="11">
+        <v>3.524</v>
+      </c>
+      <c r="S6" s="11">
+        <v>2.8069999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>20000</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="B7" s="11">
+        <v>185.93700000000001</v>
+      </c>
+      <c r="C7" s="11">
+        <v>175.24199999999999</v>
+      </c>
+      <c r="D7" s="11">
+        <v>188.38300000000001</v>
+      </c>
+      <c r="E7" s="11">
+        <v>605.02300000000002</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>467.142</v>
+      </c>
+      <c r="H7" s="11">
+        <v>4.7939999999999996</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1.915</v>
+      </c>
+      <c r="J7" s="11">
+        <v>1.4690000000000001</v>
+      </c>
+      <c r="K7" s="11">
+        <v>3.5720000000000001</v>
+      </c>
+      <c r="L7" s="11">
+        <v>386.03300000000002</v>
+      </c>
+      <c r="M7" s="11">
+        <v>268.125</v>
+      </c>
+      <c r="N7" s="11">
+        <v>123.928</v>
+      </c>
+      <c r="O7" s="11">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="P7" s="11">
+        <v>225.494</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>5.4379999999999997</v>
+      </c>
+      <c r="R7" s="11">
+        <v>2.9849999999999999</v>
+      </c>
+      <c r="S7" s="11">
+        <v>2.2170000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
         <v>24000</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="B8" s="11">
+        <v>261.738</v>
+      </c>
+      <c r="C8" s="11">
+        <v>259.67599999999999</v>
+      </c>
+      <c r="D8" s="11">
+        <v>274.63200000000001</v>
+      </c>
+      <c r="E8" s="11">
+        <v>956.49599999999998</v>
+      </c>
+      <c r="F8" s="11">
+        <v>2.3E-2</v>
+      </c>
+      <c r="G8" s="11">
+        <v>672.33799999999997</v>
+      </c>
+      <c r="H8" s="11">
+        <v>4.375</v>
+      </c>
+      <c r="I8" s="11">
+        <v>1.5329999999999999</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1.397</v>
+      </c>
+      <c r="K8" s="11">
+        <v>4.2149999999999999</v>
+      </c>
+      <c r="L8" s="11">
+        <v>564.02700000000004</v>
+      </c>
+      <c r="M8" s="11">
+        <v>378.58699999999999</v>
+      </c>
+      <c r="N8" s="11">
+        <v>172.91200000000001</v>
+      </c>
+      <c r="O8" s="11">
+        <v>3.9E-2</v>
+      </c>
+      <c r="P8" s="11">
+        <v>326.51</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>7.1029999999999998</v>
+      </c>
+      <c r="R8" s="11">
+        <v>3.464</v>
+      </c>
+      <c r="S8" s="11">
+        <v>2.6920000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
         <v>28000</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="B9" s="11">
+        <v>357.19400000000002</v>
+      </c>
+      <c r="C9" s="11">
+        <v>350.94</v>
+      </c>
+      <c r="D9" s="11">
+        <v>369.553</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1346.9079999999999</v>
+      </c>
+      <c r="F9" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G9" s="11">
+        <v>896.46699999999998</v>
+      </c>
+      <c r="H9" s="11">
+        <v>6.7030000000000003</v>
+      </c>
+      <c r="I9" s="11">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="J9" s="11">
+        <v>1.9450000000000001</v>
+      </c>
+      <c r="K9" s="11">
+        <v>3.5449999999999999</v>
+      </c>
+      <c r="L9" s="11">
+        <v>744.77599999999995</v>
+      </c>
+      <c r="M9" s="11">
+        <v>544.23199999999997</v>
+      </c>
+      <c r="N9" s="11">
+        <v>221.95699999999999</v>
+      </c>
+      <c r="O9" s="11">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="P9" s="11">
+        <v>466.74799999999999</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>7.944</v>
+      </c>
+      <c r="R9" s="11">
+        <v>3.7040000000000002</v>
+      </c>
+      <c r="S9" s="11">
+        <v>3.2189999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
         <v>32000</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="B10" s="11">
+        <v>466.34899999999999</v>
+      </c>
+      <c r="C10" s="11">
+        <v>459.60300000000001</v>
+      </c>
+      <c r="D10" s="11">
+        <v>512.48</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1816.809</v>
+      </c>
+      <c r="F10" s="11">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1171.1890000000001</v>
+      </c>
+      <c r="H10" s="11">
+        <v>7.6680000000000001</v>
+      </c>
+      <c r="I10" s="11">
+        <v>2.956</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1.66</v>
+      </c>
+      <c r="K10" s="11">
+        <v>3.452</v>
+      </c>
+      <c r="L10" s="11">
+        <v>976.27200000000005</v>
+      </c>
+      <c r="M10" s="11">
+        <v>700.28</v>
+      </c>
+      <c r="N10" s="11">
+        <v>322.48500000000001</v>
+      </c>
+      <c r="O10" s="11">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="P10" s="11">
+        <v>585.64200000000005</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>8.1750000000000007</v>
+      </c>
+      <c r="R10" s="11">
+        <v>4.0529999999999999</v>
+      </c>
+      <c r="S10" s="11">
+        <v>4.218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>36000</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+      <c r="B11" s="11">
+        <v>595.48099999999999</v>
+      </c>
+      <c r="C11" s="11">
+        <v>599.221</v>
+      </c>
+      <c r="D11" s="11">
+        <v>599.27700000000004</v>
+      </c>
+      <c r="E11" s="11">
+        <v>2338.7570000000001</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G11" s="11">
+        <v>1508.0719999999999</v>
+      </c>
+      <c r="H11" s="11">
+        <v>8.798</v>
+      </c>
+      <c r="I11" s="11">
+        <v>2.5310000000000001</v>
+      </c>
+      <c r="J11" s="11">
+        <v>2.4079999999999999</v>
+      </c>
+      <c r="K11" s="11">
+        <v>6.2050000000000001</v>
+      </c>
+      <c r="L11" s="11">
+        <v>1307.578</v>
+      </c>
+      <c r="M11" s="11">
+        <v>879.33699999999999</v>
+      </c>
+      <c r="N11" s="11">
+        <v>379.65100000000001</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0.122</v>
+      </c>
+      <c r="P11" s="11">
+        <v>780.79</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>9.5939999999999994</v>
+      </c>
+      <c r="R11" s="11">
+        <v>4.6550000000000002</v>
+      </c>
+      <c r="S11" s="11">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="12" spans="1:26" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="3"/>
@@ -4130,838 +4060,394 @@
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="13">
-        <v>8000</v>
-      </c>
-      <c r="C20" s="14">
-        <v>72.472999999999999</v>
-      </c>
-      <c r="D20" s="14">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>73.465000000000003</v>
-      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="13">
-        <v>12000</v>
-      </c>
-      <c r="C21" s="14">
-        <v>177.291</v>
-      </c>
-      <c r="D21" s="14">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="E21" s="14">
-        <v>167.935</v>
-      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="13">
-        <v>16000</v>
-      </c>
-      <c r="C22" s="14">
-        <v>352.012</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>298.31299999999999</v>
-      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="13">
-        <v>20000</v>
-      </c>
-      <c r="C23" s="14">
-        <v>605.02300000000002</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1.9E-2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>467.142</v>
-      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="13">
-        <v>24000</v>
-      </c>
-      <c r="C24" s="14">
-        <v>956.49599999999998</v>
-      </c>
-      <c r="D24" s="14">
-        <v>2.3E-2</v>
-      </c>
-      <c r="E24" s="14">
-        <v>672.33799999999997</v>
-      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="13">
-        <v>28000</v>
-      </c>
-      <c r="C25" s="14">
-        <v>1346.9079999999999</v>
-      </c>
-      <c r="D25" s="14">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E25" s="14">
-        <v>896.46699999999998</v>
-      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="13">
-        <v>32000</v>
-      </c>
-      <c r="C26" s="14">
-        <v>1816.809</v>
-      </c>
-      <c r="D26" s="14">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="E26" s="14">
-        <v>1171.1890000000001</v>
-      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="13">
-        <v>36000</v>
-      </c>
-      <c r="C27" s="14">
-        <v>2338.7570000000001</v>
-      </c>
-      <c r="D27" s="14">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>1508.0719999999999</v>
-      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="13">
-        <v>8000</v>
-      </c>
-      <c r="C31" s="14">
-        <v>23.056000000000001</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="E31" s="14">
-        <v>38.313000000000002</v>
-      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="13">
-        <v>12000</v>
-      </c>
-      <c r="C32" s="14">
-        <v>51.765000000000001</v>
-      </c>
-      <c r="D32" s="14">
-        <v>1.9E-2</v>
-      </c>
-      <c r="E32" s="14">
-        <v>86.817999999999998</v>
-      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="13">
-        <v>16000</v>
-      </c>
-      <c r="C33" s="14">
-        <v>82.046999999999997</v>
-      </c>
-      <c r="D33" s="14">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E33" s="14">
-        <v>148.87899999999999</v>
-      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="13">
-        <v>20000</v>
-      </c>
-      <c r="C34" s="14">
-        <v>123.928</v>
-      </c>
-      <c r="D34" s="14">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="E34" s="14">
-        <v>225.494</v>
-      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="13">
-        <v>24000</v>
-      </c>
-      <c r="C35" s="14">
-        <v>172.91200000000001</v>
-      </c>
-      <c r="D35" s="14">
-        <v>3.9E-2</v>
-      </c>
-      <c r="E35" s="14">
-        <v>326.51</v>
-      </c>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="13">
-        <v>28000</v>
-      </c>
-      <c r="C36" s="14">
-        <v>221.95699999999999</v>
-      </c>
-      <c r="D36" s="14">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="E36" s="14">
-        <v>466.74799999999999</v>
-      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="13">
-        <v>32000</v>
-      </c>
-      <c r="C37" s="14">
-        <v>322.48500000000001</v>
-      </c>
-      <c r="D37" s="14">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="E37" s="14">
-        <v>585.64200000000005</v>
-      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="13">
-        <v>36000</v>
-      </c>
-      <c r="C38" s="14">
-        <v>379.65100000000001</v>
-      </c>
-      <c r="D38" s="14">
-        <v>0.122</v>
-      </c>
-      <c r="E38" s="14">
-        <v>780.79</v>
-      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
     </row>
     <row r="40" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
     </row>
     <row r="41" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
     </row>
     <row r="42" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="13">
-        <v>8000</v>
-      </c>
-      <c r="C42" s="14">
-        <v>33.103999999999999</v>
-      </c>
-      <c r="D42" s="14">
-        <v>28.675000000000001</v>
-      </c>
-      <c r="E42" s="14">
-        <v>28.757999999999999</v>
-      </c>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="13">
-        <v>12000</v>
-      </c>
-      <c r="C43" s="14">
-        <v>72.576999999999998</v>
-      </c>
-      <c r="D43" s="14">
-        <v>63.32</v>
-      </c>
-      <c r="E43" s="14">
-        <v>64.200999999999993</v>
-      </c>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="13">
-        <v>16000</v>
-      </c>
-      <c r="C44" s="14">
-        <v>117.86</v>
-      </c>
-      <c r="D44" s="14">
-        <v>115.587</v>
-      </c>
-      <c r="E44" s="14">
-        <v>119.71299999999999</v>
-      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="13">
-        <v>20000</v>
-      </c>
-      <c r="C45" s="14">
-        <v>185.93700000000001</v>
-      </c>
-      <c r="D45" s="14">
-        <v>175.24199999999999</v>
-      </c>
-      <c r="E45" s="14">
-        <v>188.38300000000001</v>
-      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="13">
-        <v>24000</v>
-      </c>
-      <c r="C46" s="14">
-        <v>261.738</v>
-      </c>
-      <c r="D46" s="14">
-        <v>259.67599999999999</v>
-      </c>
-      <c r="E46" s="14">
-        <v>274.63200000000001</v>
-      </c>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="13">
-        <v>28000</v>
-      </c>
-      <c r="C47" s="14">
-        <v>357.19400000000002</v>
-      </c>
-      <c r="D47" s="14">
-        <v>350.94</v>
-      </c>
-      <c r="E47" s="14">
-        <v>369.553</v>
-      </c>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="13">
-        <v>32000</v>
-      </c>
-      <c r="C48" s="14">
-        <v>466.34899999999999</v>
-      </c>
-      <c r="D48" s="14">
-        <v>459.60300000000001</v>
-      </c>
-      <c r="E48" s="14">
-        <v>512.48</v>
-      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
     </row>
     <row r="49" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="13">
-        <v>36000</v>
-      </c>
-      <c r="C49" s="14">
-        <v>595.48099999999999</v>
-      </c>
-      <c r="D49" s="14">
-        <v>599.221</v>
-      </c>
-      <c r="E49" s="14">
-        <v>599.27700000000004</v>
-      </c>
+      <c r="B49" s="10"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="13">
-        <v>8000</v>
-      </c>
-      <c r="C53" s="14">
-        <v>1.181</v>
-      </c>
-      <c r="D53" s="14">
-        <v>67.837999999999994</v>
-      </c>
-      <c r="E53" s="14">
-        <v>45.11</v>
-      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
     </row>
     <row r="54" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="13">
-        <v>12000</v>
-      </c>
-      <c r="C54" s="14">
-        <v>2.02</v>
-      </c>
-      <c r="D54" s="14">
-        <v>176.26499999999999</v>
-      </c>
-      <c r="E54" s="14">
-        <v>94.897999999999996</v>
-      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
     </row>
     <row r="55" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="13">
-        <v>16000</v>
-      </c>
-      <c r="C55" s="14">
-        <v>2.8069999999999999</v>
-      </c>
-      <c r="D55" s="14">
-        <v>246.90899999999999</v>
-      </c>
-      <c r="E55" s="14">
-        <v>165.846</v>
-      </c>
+      <c r="B55" s="10"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="13">
-        <v>20000</v>
-      </c>
-      <c r="C56" s="14">
-        <v>3.5720000000000001</v>
-      </c>
-      <c r="D56" s="14">
-        <v>386.03300000000002</v>
-      </c>
-      <c r="E56" s="14">
-        <v>268.125</v>
-      </c>
+      <c r="B56" s="10"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="13">
-        <v>24000</v>
-      </c>
-      <c r="C57" s="14">
-        <v>4.2149999999999999</v>
-      </c>
-      <c r="D57" s="14">
-        <v>564.02700000000004</v>
-      </c>
-      <c r="E57" s="14">
-        <v>378.58699999999999</v>
-      </c>
+      <c r="B57" s="10"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="13">
-        <v>28000</v>
-      </c>
-      <c r="C58" s="14">
-        <v>3.5449999999999999</v>
-      </c>
-      <c r="D58" s="14">
-        <v>744.77599999999995</v>
-      </c>
-      <c r="E58" s="14">
-        <v>544.23199999999997</v>
-      </c>
+      <c r="B58" s="10"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
     </row>
     <row r="59" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="13">
-        <v>32000</v>
-      </c>
-      <c r="C59" s="14">
-        <v>3.452</v>
-      </c>
-      <c r="D59" s="14">
-        <v>976.27200000000005</v>
-      </c>
-      <c r="E59" s="14">
-        <v>700.28</v>
-      </c>
+      <c r="B59" s="10"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="13">
-        <v>36000</v>
-      </c>
-      <c r="C60" s="14">
-        <v>6.2050000000000001</v>
-      </c>
-      <c r="D60" s="14">
-        <v>1307.578</v>
-      </c>
-      <c r="E60" s="14">
-        <v>879.33699999999999</v>
-      </c>
+      <c r="B60" s="10"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
     </row>
     <row r="61" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
     </row>
     <row r="62" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
     </row>
     <row r="63" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
     </row>
     <row r="64" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="13">
-        <v>8000</v>
-      </c>
-      <c r="C64" s="14">
-        <v>1.7989999999999999</v>
-      </c>
-      <c r="D64" s="14">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="E64" s="14">
-        <v>0.81899999999999995</v>
-      </c>
+      <c r="B64" s="10"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
     </row>
     <row r="65" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="13">
-        <v>12000</v>
-      </c>
-      <c r="C65" s="14">
-        <v>2.5249999999999999</v>
-      </c>
-      <c r="D65" s="14">
-        <v>1.0760000000000001</v>
-      </c>
-      <c r="E65" s="14">
-        <v>0.93700000000000006</v>
-      </c>
+      <c r="B65" s="10"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="13">
-        <v>16000</v>
-      </c>
-      <c r="C66" s="14">
-        <v>3.6989999999999998</v>
-      </c>
-      <c r="D66" s="14">
-        <v>1.4350000000000001</v>
-      </c>
-      <c r="E66" s="14">
-        <v>1.3340000000000001</v>
-      </c>
+      <c r="B66" s="10"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="13">
-        <v>20000</v>
-      </c>
-      <c r="C67" s="14">
-        <v>4.7939999999999996</v>
-      </c>
-      <c r="D67" s="14">
-        <v>1.915</v>
-      </c>
-      <c r="E67" s="14">
-        <v>1.4690000000000001</v>
-      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
     </row>
     <row r="68" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="13">
-        <v>24000</v>
-      </c>
-      <c r="C68" s="14">
-        <v>4.375</v>
-      </c>
-      <c r="D68" s="14">
-        <v>1.5329999999999999</v>
-      </c>
-      <c r="E68" s="14">
-        <v>1.397</v>
-      </c>
+      <c r="B68" s="10"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
     </row>
     <row r="69" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="13">
-        <v>28000</v>
-      </c>
-      <c r="C69" s="14">
-        <v>6.7030000000000003</v>
-      </c>
-      <c r="D69" s="14">
-        <v>3.1589999999999998</v>
-      </c>
-      <c r="E69" s="14">
-        <v>1.9450000000000001</v>
-      </c>
+      <c r="B69" s="10"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
     </row>
     <row r="70" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="13">
-        <v>32000</v>
-      </c>
-      <c r="C70" s="14">
-        <v>7.6680000000000001</v>
-      </c>
-      <c r="D70" s="14">
-        <v>2.956</v>
-      </c>
-      <c r="E70" s="14">
-        <v>1.66</v>
-      </c>
+      <c r="B70" s="10"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
     </row>
     <row r="71" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="13">
-        <v>36000</v>
-      </c>
-      <c r="C71" s="14">
-        <v>8.798</v>
-      </c>
-      <c r="D71" s="14">
-        <v>2.5310000000000001</v>
-      </c>
-      <c r="E71" s="14">
-        <v>2.4079999999999999</v>
-      </c>
+      <c r="B71" s="10"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
     </row>
     <row r="73" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
     </row>
     <row r="74" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>17</v>
-      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
     </row>
     <row r="75" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="13">
-        <v>8000</v>
-      </c>
-      <c r="C75" s="14">
-        <v>2.3039999999999998</v>
-      </c>
-      <c r="D75" s="14">
-        <v>1.9810000000000001</v>
-      </c>
-      <c r="E75" s="14">
-        <v>1.734</v>
-      </c>
+      <c r="B75" s="10"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
     </row>
     <row r="76" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="13">
-        <v>12000</v>
-      </c>
-      <c r="C76" s="14">
-        <v>2.1040000000000001</v>
-      </c>
-      <c r="D76" s="14">
-        <v>1.3029999999999999</v>
-      </c>
-      <c r="E76" s="14">
-        <v>1.5680000000000001</v>
-      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
     </row>
     <row r="77" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="13">
-        <v>16000</v>
-      </c>
-      <c r="C77" s="14">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="D77" s="14">
-        <v>3.524</v>
-      </c>
-      <c r="E77" s="14">
-        <v>2.8069999999999999</v>
-      </c>
+      <c r="B77" s="10"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
     </row>
     <row r="78" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="13">
-        <v>20000</v>
-      </c>
-      <c r="C78" s="14">
-        <v>5.4379999999999997</v>
-      </c>
-      <c r="D78" s="14">
-        <v>2.9849999999999999</v>
-      </c>
-      <c r="E78" s="14">
-        <v>2.2170000000000001</v>
-      </c>
+      <c r="B78" s="10"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
     </row>
     <row r="79" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="13">
-        <v>24000</v>
-      </c>
-      <c r="C79" s="14">
-        <v>7.1029999999999998</v>
-      </c>
-      <c r="D79" s="14">
-        <v>3.464</v>
-      </c>
-      <c r="E79" s="14">
-        <v>2.6920000000000002</v>
-      </c>
+      <c r="B79" s="10"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
     </row>
     <row r="80" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="13">
-        <v>28000</v>
-      </c>
-      <c r="C80" s="14">
-        <v>7.944</v>
-      </c>
-      <c r="D80" s="14">
-        <v>3.7040000000000002</v>
-      </c>
-      <c r="E80" s="14">
-        <v>3.2189999999999999</v>
-      </c>
+      <c r="B80" s="10"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
     </row>
     <row r="81" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="13">
-        <v>32000</v>
-      </c>
-      <c r="C81" s="14">
-        <v>8.1750000000000007</v>
-      </c>
-      <c r="D81" s="14">
-        <v>4.0529999999999999</v>
-      </c>
-      <c r="E81" s="14">
-        <v>4.218</v>
-      </c>
+      <c r="B81" s="10"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
     </row>
     <row r="82" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="13">
-        <v>36000</v>
-      </c>
-      <c r="C82" s="14">
-        <v>9.5939999999999994</v>
-      </c>
-      <c r="D82" s="14">
-        <v>4.6550000000000002</v>
-      </c>
-      <c r="E82" s="14">
-        <v>4.7</v>
-      </c>
+      <c r="B82" s="10"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
     </row>
     <row r="83" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5882,7 +5368,9 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
